--- a/Financial Analysis/Models (Retail) {2024}.xlsx
+++ b/Financial Analysis/Models (Retail) {2024}.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E31180-44CD-46D7-A475-076D3915B937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0657C0A3-8516-40F6-B3B0-7ED124143A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8DE2C096-8306-4635-BAD7-DE2F1A3674DA}"/>
   </bookViews>
@@ -556,28 +556,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>95.91</v>
+            <v>99.35</v>
           </cell>
           <cell r="E3">
-            <v>45772</v>
+            <v>45904</v>
           </cell>
           <cell r="G3">
-            <v>45792</v>
+            <v>45981</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>768891.28799999994</v>
+            <v>792107.61499999987</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-30030</v>
+            <v>-34057</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>798921.28799999994</v>
+            <v>826164.61499999987</v>
           </cell>
         </row>
       </sheetData>
@@ -595,16 +595,16 @@
             <v>19436</v>
           </cell>
           <cell r="Z13">
-            <v>23548.148100000006</v>
+            <v>21328.850996000001</v>
           </cell>
           <cell r="AA13">
-            <v>29771.666883000013</v>
+            <v>26422.735906899998</v>
           </cell>
           <cell r="AB13">
-            <v>30390.350849909999</v>
+            <v>32523.971098128004</v>
           </cell>
           <cell r="AC13">
-            <v>31021.641002450713</v>
+            <v>33176.054117290558</v>
           </cell>
         </row>
         <row r="17">
@@ -632,7 +632,7 @@
         </row>
         <row r="25">
           <cell r="AM25">
-            <v>-0.29027089149658136</v>
+            <v>-0.28239532428978786</v>
           </cell>
         </row>
         <row r="26">
@@ -1434,77 +1434,77 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>630.4</v>
+            <v>520.79999999999995</v>
           </cell>
           <cell r="E3">
-            <v>45633</v>
+            <v>45904</v>
           </cell>
           <cell r="G3">
-            <v>45680</v>
+            <v>46044</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>315263.03999999998</v>
+            <v>259566.71999999997</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-13621</v>
+            <v>-11306</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>328884.03999999998</v>
+            <v>270872.71999999997</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="AA3">
-            <v>85370.434999999998</v>
+          <cell r="AC3">
+            <v>84683</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="Z16">
+          <cell r="AB16">
             <v>15174</v>
           </cell>
-          <cell r="AA16">
-            <v>14781.352341499993</v>
-          </cell>
-          <cell r="AB16">
-            <v>15309.741958159999</v>
-          </cell>
           <cell r="AC16">
-            <v>15771.019859244794</v>
+            <v>12550</v>
           </cell>
           <cell r="AD16">
-            <v>16083.641932311391</v>
+            <v>12093.875180000003</v>
           </cell>
           <cell r="AE16">
-            <v>16403.087535732939</v>
+            <v>13628.273855011206</v>
+          </cell>
+          <cell r="AF16">
+            <v>14521.585934581055</v>
+          </cell>
+          <cell r="AG16">
+            <v>14814.665475592677</v>
           </cell>
         </row>
         <row r="20">
-          <cell r="Z20">
+          <cell r="AB20">
             <v>8.8010204081632626E-2</v>
           </cell>
-          <cell r="AA20">
-            <v>-9.0834329622880849E-3</v>
+          <cell r="AC20">
+            <v>-1.7062667579770818E-2</v>
           </cell>
         </row>
         <row r="23">
-          <cell r="AO23">
+          <cell r="AQ23">
             <v>0.05</v>
           </cell>
         </row>
         <row r="29">
-          <cell r="AO29">
-            <v>-5.705492944318058E-2</v>
+          <cell r="AQ29">
+            <v>2.6905095757119524E-2</v>
           </cell>
         </row>
         <row r="30">
-          <cell r="AO30" t="str">
+          <cell r="AQ30" t="str">
             <v>Fairly valued</v>
           </cell>
         </row>
@@ -2275,28 +2275,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>126.5</v>
+            <v>140.91</v>
           </cell>
           <cell r="E3">
-            <v>45772</v>
+            <v>45909</v>
           </cell>
           <cell r="G3">
-            <v>45798</v>
+            <v>45980</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>141313.15</v>
+            <v>156818.739</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2469</v>
+            <v>1772</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>138844.15</v>
+            <v>155046.739</v>
           </cell>
         </row>
       </sheetData>
@@ -2314,16 +2314,16 @@
             <v>4864</v>
           </cell>
           <cell r="AW11">
-            <v>5404.1280000000015</v>
+            <v>5080.6246999999976</v>
           </cell>
           <cell r="AX11">
-            <v>5319.3811200000018</v>
+            <v>5797.5631012499998</v>
           </cell>
           <cell r="AY11">
-            <v>5424.3225216000028</v>
+            <v>5918.1293075793765</v>
           </cell>
           <cell r="AZ11">
-            <v>5532.7981253760017</v>
+            <v>6036.5265058132481</v>
           </cell>
         </row>
         <row r="15">
@@ -2341,7 +2341,7 @@
         </row>
         <row r="24">
           <cell r="BJ24">
-            <v>-0.46135684426871026</v>
+            <v>-0.44545388548595966</v>
           </cell>
         </row>
         <row r="25">
@@ -2485,18 +2485,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>58.29</v>
+            <v>74.23</v>
           </cell>
           <cell r="E3">
-            <v>45772</v>
+            <v>45909</v>
           </cell>
           <cell r="G3">
-            <v>45834</v>
+            <v>45930</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>86036.04</v>
+            <v>109630.28700000001</v>
           </cell>
         </row>
         <row r="8">
@@ -2506,57 +2506,57 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>84603.04</v>
+            <v>108197.28700000001</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="AR3">
-            <v>46935.58</v>
+          <cell r="AV3">
+            <v>46309</v>
           </cell>
         </row>
         <row r="13">
-          <cell r="AQ13">
+          <cell r="AU13">
             <v>5700</v>
           </cell>
-          <cell r="AR13">
-            <v>4158.7407180000018</v>
-          </cell>
-          <cell r="AS13">
-            <v>5447.0607473599994</v>
-          </cell>
-          <cell r="AT13">
-            <v>5501.5313548336017</v>
-          </cell>
-          <cell r="AU13">
-            <v>5556.5466683819395</v>
-          </cell>
           <cell r="AV13">
-            <v>5612.1121350657577</v>
+            <v>3219</v>
+          </cell>
+          <cell r="AW13">
+            <v>4477.8666000000003</v>
+          </cell>
+          <cell r="AX13">
+            <v>5460.087105999999</v>
+          </cell>
+          <cell r="AY13">
+            <v>5809.9953370599997</v>
+          </cell>
+          <cell r="AZ13">
+            <v>5868.0952904306032</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="AP17">
+          <cell r="AT17">
             <v>9.6488974523656568E-2</v>
           </cell>
-          <cell r="AQ17">
+          <cell r="AU17">
             <v>2.8310912392370824E-3</v>
           </cell>
         </row>
         <row r="20">
-          <cell r="BE20">
+          <cell r="BI20">
             <v>7.0000000000000007E-2</v>
           </cell>
         </row>
         <row r="26">
-          <cell r="BE26">
-            <v>-0.11787291905287733</v>
+          <cell r="BI26">
+            <v>-0.28255388577382867</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="BE27" t="str">
-            <v>Slightly overvalued</v>
+          <cell r="BI27" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -3394,32 +3394,32 @@
       <c r="M3" s="3"/>
       <c r="N3" s="6">
         <f t="shared" ref="N3:U3" si="0">TRIMMEAN(N4:N1048576,80%)</f>
-        <v>21.284290499890915</v>
+        <v>20.386889840475803</v>
       </c>
       <c r="O3" s="6">
         <f t="shared" si="0"/>
-        <v>26.251166047313312</v>
+        <v>29.924485010131235</v>
       </c>
       <c r="P3" s="6">
         <f t="shared" si="0"/>
-        <v>24.033030906710014</v>
+        <v>25.773334557327757</v>
       </c>
       <c r="Q3" s="6">
         <f t="shared" si="0"/>
-        <v>19.253520436640294</v>
+        <v>19.658935892482816</v>
       </c>
       <c r="R3" s="6">
         <f t="shared" si="0"/>
-        <v>18.680084366164444</v>
+        <v>18.643116186594863</v>
       </c>
       <c r="S3" s="6">
         <f t="shared" si="0"/>
-        <v>17.808846254601399</v>
+        <v>18.224907671861427</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="21">
         <f t="shared" si="0"/>
-        <v>0.98589961550171934</v>
+        <v>0.99923487105066666</v>
       </c>
       <c r="V3" s="7">
         <f>TRIMMEAN(V4:V1048576,80%)</f>
@@ -3463,19 +3463,19 @@
       </c>
       <c r="D4" s="15">
         <f>[1]Main!$D$3</f>
-        <v>95.91</v>
+        <v>99.35</v>
       </c>
       <c r="E4" s="12">
         <f>[1]Main!$D$5</f>
-        <v>768891.28799999994</v>
+        <v>792107.61499999987</v>
       </c>
       <c r="F4" s="12">
         <f>[1]Main!$D$8</f>
-        <v>-30030</v>
+        <v>-34057</v>
       </c>
       <c r="G4" s="12">
         <f>[1]Main!$D$9</f>
-        <v>798921.28799999994</v>
+        <v>826164.61499999987</v>
       </c>
       <c r="H4" s="12">
         <f>[1]Model!X13</f>
@@ -3487,43 +3487,43 @@
       </c>
       <c r="J4" s="12">
         <f>[1]Model!Z13</f>
-        <v>23548.148100000006</v>
+        <v>21328.850996000001</v>
       </c>
       <c r="K4" s="12">
         <f>[1]Model!AA13</f>
-        <v>29771.666883000013</v>
+        <v>26422.735906899998</v>
       </c>
       <c r="L4" s="12">
         <f>[1]Model!AB13</f>
-        <v>30390.350849909999</v>
+        <v>32523.971098128004</v>
       </c>
       <c r="M4" s="12">
         <f>[1]Model!AC13</f>
-        <v>31021.641002450713</v>
+        <v>33176.054117290558</v>
       </c>
       <c r="N4" s="11">
         <f t="shared" ref="N4" si="2">$G4/H4</f>
-        <v>51.506755721745854</v>
+        <v>53.263143253175159</v>
       </c>
       <c r="O4" s="11">
         <f t="shared" ref="O4" si="3">$G4/I4</f>
-        <v>41.105231940728544</v>
+        <v>42.506926065033952</v>
       </c>
       <c r="P4" s="11">
         <f t="shared" ref="P4" si="4">$G4/J4</f>
-        <v>33.927138754490834</v>
+        <v>38.734604839001328</v>
       </c>
       <c r="Q4" s="11">
         <f t="shared" ref="Q4" si="5">$G4/K4</f>
-        <v>26.834953217086873</v>
+        <v>31.267186634683668</v>
       </c>
       <c r="R4" s="11">
         <f t="shared" ref="R4" si="6">$G4/L4</f>
-        <v>26.288649708115035</v>
+        <v>25.401714092887993</v>
       </c>
       <c r="S4" s="11">
         <f t="shared" ref="S4" si="7">$G4/M4</f>
-        <v>25.753675891513446</v>
+        <v>24.902437525547164</v>
       </c>
       <c r="T4" s="12">
         <f>[1]Model!$Y$3</f>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="U4" s="20">
         <f>G4/T4</f>
-        <v>1.1731848542919447</v>
+        <v>1.213190620938787</v>
       </c>
       <c r="V4" s="13">
         <f>[1]Model!X$17</f>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AA4" s="13">
         <f>[1]Model!$AM$25</f>
-        <v>-0.29027089149658136</v>
+        <v>-0.28239532428978786</v>
       </c>
       <c r="AB4" s="9" t="str">
         <f>[1]Model!$AM$26</f>
@@ -3569,11 +3569,11 @@
       </c>
       <c r="AF4" s="14">
         <f>[1]Main!$E$3</f>
-        <v>45772</v>
+        <v>45904</v>
       </c>
       <c r="AG4" s="14">
         <f>[1]Main!$G$3</f>
-        <v>45792</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.3">
@@ -3585,96 +3585,96 @@
       </c>
       <c r="D5" s="18">
         <f>[2]Main!$D$3</f>
-        <v>630.4</v>
+        <v>520.79999999999995</v>
       </c>
       <c r="E5" s="12">
         <f>[2]Main!$D$5</f>
-        <v>315263.03999999998</v>
+        <v>259566.71999999997</v>
       </c>
       <c r="F5" s="12">
         <f>[2]Main!$D$8</f>
-        <v>-13621</v>
+        <v>-11306</v>
       </c>
       <c r="G5" s="12">
         <f>[2]Main!$D$9</f>
-        <v>328884.03999999998</v>
+        <v>270872.71999999997</v>
       </c>
       <c r="H5" s="12">
-        <f>[2]Model!Z16</f>
+        <f>[2]Model!AB16</f>
         <v>15174</v>
       </c>
       <c r="I5" s="12">
-        <f>[2]Model!AA16</f>
-        <v>14781.352341499993</v>
+        <f>[2]Model!AC16</f>
+        <v>12550</v>
       </c>
       <c r="J5" s="12">
-        <f>[2]Model!AB16</f>
-        <v>15309.741958159999</v>
+        <f>[2]Model!AD16</f>
+        <v>12093.875180000003</v>
       </c>
       <c r="K5" s="12">
-        <f>[2]Model!AC16</f>
-        <v>15771.019859244794</v>
+        <f>[2]Model!AE16</f>
+        <v>13628.273855011206</v>
       </c>
       <c r="L5" s="12">
-        <f>[2]Model!AD16</f>
-        <v>16083.641932311391</v>
+        <f>[2]Model!AF16</f>
+        <v>14521.585934581055</v>
       </c>
       <c r="M5" s="12">
-        <f>[2]Model!AE16</f>
-        <v>16403.087535732939</v>
+        <f>[2]Model!AG16</f>
+        <v>14814.665475592677</v>
       </c>
       <c r="N5" s="11">
         <f t="shared" ref="N5:S5" si="8">$G5/H5</f>
-        <v>21.674182153683933</v>
+        <v>17.851108475023064</v>
       </c>
       <c r="O5" s="11">
         <f t="shared" si="8"/>
-        <v>22.249928991722097</v>
+        <v>21.583483665338644</v>
       </c>
       <c r="P5" s="11">
         <f t="shared" si="8"/>
-        <v>21.482010663459079</v>
+        <v>22.397512457210585</v>
       </c>
       <c r="Q5" s="11">
         <f t="shared" si="8"/>
-        <v>20.853695127852614</v>
+        <v>19.875790792125759</v>
       </c>
       <c r="R5" s="11">
         <f t="shared" si="8"/>
-        <v>20.448356248175678</v>
+        <v>18.653108635672897</v>
       </c>
       <c r="S5" s="11">
         <f t="shared" si="8"/>
-        <v>20.050130152847743</v>
+        <v>18.284092910924361</v>
       </c>
       <c r="T5" s="12">
-        <f>[2]Model!$AA$3</f>
-        <v>85370.434999999998</v>
+        <f>[2]Model!$AC$3</f>
+        <v>84683</v>
       </c>
       <c r="U5" s="20">
         <f t="shared" ref="U5:U7" si="9">G5/T5</f>
-        <v>3.8524348622564708</v>
+        <v>3.19866702880153</v>
       </c>
       <c r="V5" s="13">
-        <f>[2]Model!Z$20</f>
+        <f>[2]Model!AB$20</f>
         <v>8.8010204081632626E-2</v>
       </c>
       <c r="W5" s="13">
-        <f>[2]Model!AA$20</f>
-        <v>-9.0834329622880849E-3</v>
+        <f>[2]Model!AC$20</f>
+        <v>-1.7062667579770818E-2</v>
       </c>
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
       <c r="Z5" s="13">
-        <f>[2]Model!$AO$23</f>
+        <f>[2]Model!$AQ$23</f>
         <v>0.05</v>
       </c>
       <c r="AA5" s="13">
-        <f>[2]Model!$AO$29</f>
-        <v>-5.705492944318058E-2</v>
+        <f>[2]Model!$AQ$29</f>
+        <v>2.6905095757119524E-2</v>
       </c>
       <c r="AB5" s="9" t="str">
-        <f>[2]Model!$AO$30</f>
+        <f>[2]Model!$AQ$30</f>
         <v>Fairly valued</v>
       </c>
       <c r="AC5" s="9" t="s">
@@ -3685,11 +3685,11 @@
       </c>
       <c r="AF5" s="14">
         <f>[2]Main!$E$3</f>
-        <v>45633</v>
+        <v>45904</v>
       </c>
       <c r="AG5" s="14">
         <f>[2]Main!$G$3</f>
-        <v>45680</v>
+        <v>46044</v>
       </c>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.3">
@@ -3701,19 +3701,19 @@
       </c>
       <c r="D6" s="15">
         <f>[3]Main!$D$3</f>
-        <v>126.5</v>
+        <v>140.91</v>
       </c>
       <c r="E6" s="12">
         <f>[3]Main!$D$5</f>
-        <v>141313.15</v>
+        <v>156818.739</v>
       </c>
       <c r="F6" s="12">
         <f>[3]Main!$D$8</f>
-        <v>2469</v>
+        <v>1772</v>
       </c>
       <c r="G6" s="12">
         <f>[3]Main!$D$9</f>
-        <v>138844.15</v>
+        <v>155046.739</v>
       </c>
       <c r="H6" s="12">
         <f>[3]Model!AU$11</f>
@@ -3725,43 +3725,43 @@
       </c>
       <c r="J6" s="12">
         <f>[3]Model!AW$11</f>
-        <v>5404.1280000000015</v>
+        <v>5080.6246999999976</v>
       </c>
       <c r="K6" s="12">
         <f>[3]Model!AX$11</f>
-        <v>5319.3811200000018</v>
+        <v>5797.5631012499998</v>
       </c>
       <c r="L6" s="12">
         <f>[3]Model!AY$11</f>
-        <v>5424.3225216000028</v>
+        <v>5918.1293075793765</v>
       </c>
       <c r="M6" s="12">
         <f>[3]Model!AZ$11</f>
-        <v>5532.7981253760017</v>
+        <v>6036.5265058132481</v>
       </c>
       <c r="N6" s="11">
         <f t="shared" ref="N6:S6" si="10">$G6/H6</f>
-        <v>31.033560572194901</v>
+        <v>34.655060125167637</v>
       </c>
       <c r="O6" s="11">
         <f t="shared" si="10"/>
-        <v>28.545261101973683</v>
+        <v>31.876385485197368</v>
       </c>
       <c r="P6" s="11">
         <f t="shared" si="10"/>
-        <v>25.692239340000821</v>
+        <v>30.51725883236368</v>
       </c>
       <c r="Q6" s="11">
         <f t="shared" si="10"/>
-        <v>26.101560852251914</v>
+        <v>26.743432765151052</v>
       </c>
       <c r="R6" s="11">
         <f t="shared" si="10"/>
-        <v>25.596588227767359</v>
+        <v>26.198606171283028</v>
       </c>
       <c r="S6" s="11">
         <f t="shared" si="10"/>
-        <v>25.094743537306329</v>
+        <v>25.684760739588921</v>
       </c>
       <c r="T6" s="12">
         <f>[3]Model!$AV$3</f>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="U6" s="20">
         <f t="shared" si="9"/>
-        <v>2.4635228885734564</v>
+        <v>2.7510067246273953</v>
       </c>
       <c r="V6" s="13">
         <f>[3]Model!AU$15</f>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AA6" s="13">
         <f>[3]Model!$BJ$24</f>
-        <v>-0.46135684426871026</v>
+        <v>-0.44545388548595966</v>
       </c>
       <c r="AB6" s="9" t="str">
         <f>[3]Model!$BJ$25</f>
@@ -3801,11 +3801,11 @@
       </c>
       <c r="AF6" s="14">
         <f>[3]Main!$E$3</f>
-        <v>45772</v>
+        <v>45909</v>
       </c>
       <c r="AG6" s="14">
         <f>[3]Main!$G$3</f>
-        <v>45798</v>
+        <v>45980</v>
       </c>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.3">
@@ -3817,11 +3817,11 @@
       </c>
       <c r="D7" s="15">
         <f>[4]Main!$D$3</f>
-        <v>58.29</v>
+        <v>74.23</v>
       </c>
       <c r="E7" s="12">
         <f>[4]Main!$D$5</f>
-        <v>86036.04</v>
+        <v>109630.28700000001</v>
       </c>
       <c r="F7" s="12">
         <f>[4]Main!$D$8</f>
@@ -3829,85 +3829,85 @@
       </c>
       <c r="G7" s="12">
         <f>[4]Main!$D$9</f>
-        <v>84603.04</v>
+        <v>108197.28700000001</v>
       </c>
       <c r="H7" s="12">
-        <f>[4]Model!AQ13</f>
+        <f>[4]Model!AU13</f>
         <v>5700</v>
       </c>
       <c r="I7" s="12">
-        <f>[4]Model!AR13</f>
-        <v>4158.7407180000018</v>
+        <f>[4]Model!AV13</f>
+        <v>3219</v>
       </c>
       <c r="J7" s="12">
-        <f>[4]Model!AS13</f>
-        <v>5447.0607473599994</v>
+        <f>[4]Model!AW13</f>
+        <v>4477.8666000000003</v>
       </c>
       <c r="K7" s="12">
-        <f>[4]Model!AT13</f>
-        <v>5501.5313548336017</v>
+        <f>[4]Model!AX13</f>
+        <v>5460.087105999999</v>
       </c>
       <c r="L7" s="12">
-        <f>[4]Model!AU13</f>
-        <v>5556.5466683819395</v>
+        <f>[4]Model!AY13</f>
+        <v>5809.9953370599997</v>
       </c>
       <c r="M7" s="12">
-        <f>[4]Model!AV13</f>
-        <v>5612.1121350657577</v>
+        <f>[4]Model!AZ13</f>
+        <v>5868.0952904306032</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" ref="N7:S7" si="11">$G7/H7</f>
-        <v>14.842638596491227</v>
+        <v>18.981980175438597</v>
       </c>
       <c r="O7" s="11">
         <f t="shared" si="11"/>
-        <v>20.343427430764862</v>
+        <v>33.612080459770119</v>
       </c>
       <c r="P7" s="11">
         <f t="shared" si="11"/>
-        <v>15.531870108297239</v>
+        <v>24.162686534699361</v>
       </c>
       <c r="Q7" s="11">
         <f t="shared" si="11"/>
-        <v>15.378089216135875</v>
+        <v>19.816036795659141</v>
       </c>
       <c r="R7" s="11">
         <f t="shared" si="11"/>
-        <v>15.225830907065216</v>
+        <v>18.622611675752307</v>
       </c>
       <c r="S7" s="11">
         <f t="shared" si="11"/>
-        <v>15.075080106005169</v>
+        <v>18.438229381932967</v>
       </c>
       <c r="T7" s="12">
-        <f>[4]Model!$AR$3</f>
-        <v>46935.58</v>
+        <f>[4]Model!$AV$3</f>
+        <v>46309</v>
       </c>
       <c r="U7" s="20">
         <f t="shared" si="9"/>
-        <v>1.8025353047730526</v>
+        <v>2.3364202854736664</v>
       </c>
       <c r="V7" s="13">
-        <f>[4]Model!AP$17</f>
+        <f>[4]Model!AT$17</f>
         <v>9.6488974523656568E-2</v>
       </c>
       <c r="W7" s="13">
-        <f>[4]Model!AQ$17</f>
+        <f>[4]Model!AU$17</f>
         <v>2.8310912392370824E-3</v>
       </c>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
       <c r="Z7" s="13">
-        <f>[4]Model!$BE$20</f>
+        <f>[4]Model!$BI$20</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AA7" s="13">
-        <f>[4]Model!$BE$26</f>
-        <v>-0.11787291905287733</v>
+        <f>[4]Model!$BI$26</f>
+        <v>-0.28255388577382867</v>
       </c>
       <c r="AB7" s="9" t="str">
-        <f>[4]Model!$BE$27</f>
-        <v>Slightly overvalued</v>
+        <f>[4]Model!$BI$27</f>
+        <v>Overvalued</v>
       </c>
       <c r="AC7" s="9" t="s">
         <v>78</v>
@@ -3917,11 +3917,11 @@
       </c>
       <c r="AF7" s="14">
         <f>[4]Main!$E$3</f>
-        <v>45772</v>
+        <v>45909</v>
       </c>
       <c r="AG7" s="14">
         <f>[4]Main!$G$3</f>
-        <v>45834</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.3">

--- a/Financial Analysis/Models (Retail) {2024}.xlsx
+++ b/Financial Analysis/Models (Retail) {2024}.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0657C0A3-8516-40F6-B3B0-7ED124143A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258FC5F6-03E8-4865-9BD2-D3AC17ADB786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8DE2C096-8306-4635-BAD7-DE2F1A3674DA}"/>
   </bookViews>
@@ -2485,28 +2485,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>74.23</v>
+            <v>74.84</v>
           </cell>
           <cell r="E3">
-            <v>45909</v>
+            <v>45932</v>
           </cell>
           <cell r="G3">
-            <v>45930</v>
+            <v>46009</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>109630.28700000001</v>
+            <v>110628.48800000001</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>1433</v>
+            <v>575</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>108197.28700000001</v>
+            <v>110053.48800000001</v>
           </cell>
         </row>
       </sheetData>
@@ -2524,16 +2524,16 @@
             <v>3219</v>
           </cell>
           <cell r="AW13">
-            <v>4477.8666000000003</v>
+            <v>3486.365211999997</v>
           </cell>
           <cell r="AX13">
-            <v>5460.087105999999</v>
+            <v>5037.1640089999983</v>
           </cell>
           <cell r="AY13">
-            <v>5809.9953370599997</v>
+            <v>5800.8583990900024</v>
           </cell>
           <cell r="AZ13">
-            <v>5868.0952904306032</v>
+            <v>5858.866983080904</v>
           </cell>
         </row>
         <row r="17">
@@ -2551,7 +2551,7 @@
         </row>
         <row r="26">
           <cell r="BI26">
-            <v>-0.28255388577382867</v>
+            <v>-0.30866786966606552</v>
           </cell>
         </row>
         <row r="27">
@@ -3394,27 +3394,27 @@
       <c r="M3" s="3"/>
       <c r="N3" s="6">
         <f t="shared" ref="N3:U3" si="0">TRIMMEAN(N4:N1048576,80%)</f>
-        <v>20.386889840475803</v>
+        <v>20.495439606557678</v>
       </c>
       <c r="O3" s="6">
         <f t="shared" si="0"/>
-        <v>29.924485010131235</v>
+        <v>30.068644764713405</v>
       </c>
       <c r="P3" s="6">
         <f t="shared" si="0"/>
-        <v>25.773334557327757</v>
+        <v>27.361977631743837</v>
       </c>
       <c r="Q3" s="6">
         <f t="shared" si="0"/>
-        <v>19.658935892482816</v>
+        <v>20.011255133150552</v>
       </c>
       <c r="R3" s="6">
         <f t="shared" si="0"/>
-        <v>18.643116186594863</v>
+        <v>18.730446134522854</v>
       </c>
       <c r="S3" s="6">
         <f t="shared" si="0"/>
-        <v>18.224907671861427</v>
+        <v>18.233608679559865</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="21">
@@ -3817,19 +3817,19 @@
       </c>
       <c r="D7" s="15">
         <f>[4]Main!$D$3</f>
-        <v>74.23</v>
+        <v>74.84</v>
       </c>
       <c r="E7" s="12">
         <f>[4]Main!$D$5</f>
-        <v>109630.28700000001</v>
+        <v>110628.48800000001</v>
       </c>
       <c r="F7" s="12">
         <f>[4]Main!$D$8</f>
-        <v>1433</v>
+        <v>575</v>
       </c>
       <c r="G7" s="12">
         <f>[4]Main!$D$9</f>
-        <v>108197.28700000001</v>
+        <v>110053.48800000001</v>
       </c>
       <c r="H7" s="12">
         <f>[4]Model!AU13</f>
@@ -3841,43 +3841,43 @@
       </c>
       <c r="J7" s="12">
         <f>[4]Model!AW13</f>
-        <v>4477.8666000000003</v>
+        <v>3486.365211999997</v>
       </c>
       <c r="K7" s="12">
         <f>[4]Model!AX13</f>
-        <v>5460.087105999999</v>
+        <v>5037.1640089999983</v>
       </c>
       <c r="L7" s="12">
         <f>[4]Model!AY13</f>
-        <v>5809.9953370599997</v>
+        <v>5800.8583990900024</v>
       </c>
       <c r="M7" s="12">
         <f>[4]Model!AZ13</f>
-        <v>5868.0952904306032</v>
+        <v>5858.866983080904</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" ref="N7:S7" si="11">$G7/H7</f>
-        <v>18.981980175438597</v>
+        <v>19.307629473684212</v>
       </c>
       <c r="O7" s="11">
         <f t="shared" si="11"/>
-        <v>33.612080459770119</v>
+        <v>34.18871947809879</v>
       </c>
       <c r="P7" s="11">
         <f t="shared" si="11"/>
-        <v>24.162686534699361</v>
+        <v>31.566827141688478</v>
       </c>
       <c r="Q7" s="11">
         <f t="shared" si="11"/>
-        <v>19.816036795659141</v>
+        <v>21.848303490488956</v>
       </c>
       <c r="R7" s="11">
         <f t="shared" si="11"/>
-        <v>18.622611675752307</v>
+        <v>18.971931467464266</v>
       </c>
       <c r="S7" s="11">
         <f t="shared" si="11"/>
-        <v>18.438229381932967</v>
+        <v>18.784090561845805</v>
       </c>
       <c r="T7" s="12">
         <f>[4]Model!$AV$3</f>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="U7" s="20">
         <f t="shared" si="9"/>
-        <v>2.3364202854736664</v>
+        <v>2.3765032283141507</v>
       </c>
       <c r="V7" s="13">
         <f>[4]Model!AT$17</f>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AA7" s="13">
         <f>[4]Model!$BI$26</f>
-        <v>-0.28255388577382867</v>
+        <v>-0.30866786966606552</v>
       </c>
       <c r="AB7" s="9" t="str">
         <f>[4]Model!$BI$27</f>
@@ -3917,11 +3917,11 @@
       </c>
       <c r="AF7" s="14">
         <f>[4]Main!$E$3</f>
-        <v>45909</v>
+        <v>45932</v>
       </c>
       <c r="AG7" s="14">
         <f>[4]Main!$G$3</f>
-        <v>45930</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.3">
